--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepOtherInvestTargetInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepOtherInvestTargetInfo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\华夏\需求文档\需求确认材料\数据补录模板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\huaxia\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="1355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="1356">
   <si>
     <t>公共信息（必填）</t>
   </si>
@@ -5329,6 +5329,10 @@
   </si>
   <si>
     <t>是否为债转股</t>
+  </si>
+  <si>
+    <t>X01现金</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6114,6 +6118,13 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6135,27 +6146,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6163,6 +6153,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6189,40 +6191,28 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6235,6 +6225,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6242,6 +6241,18 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6251,13 +6262,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6609,7 +6613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.75" style="60" customWidth="1"/>
@@ -6625,7 +6629,7 @@
     <col min="12" max="12" width="17.625" style="60" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.75" style="60" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="22" style="71" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.25" style="119" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.25" style="73" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.5" style="60" customWidth="1"/>
     <col min="17" max="17" width="35.375" style="60" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="38.5" style="60" bestFit="1" customWidth="1"/>
@@ -6650,51 +6654,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" s="58" customFormat="1" ht="14.25" thickBot="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="76" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="78" t="s">
         <v>1326</v>
       </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-      <c r="X1" s="77"/>
-      <c r="Y1" s="77"/>
-      <c r="Z1" s="77"/>
-      <c r="AA1" s="77"/>
-      <c r="AB1" s="77"/>
-      <c r="AC1" s="77"/>
-      <c r="AD1" s="77"/>
-      <c r="AE1" s="77"/>
-      <c r="AF1" s="77"/>
-      <c r="AG1" s="77"/>
-      <c r="AH1" s="77"/>
-      <c r="AI1" s="77"/>
-      <c r="AJ1" s="78"/>
-      <c r="AK1" s="75" t="s">
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="80"/>
+      <c r="AK1" s="77" t="s">
         <v>1238</v>
       </c>
-      <c r="AL1" s="75"/>
-      <c r="AM1" s="75"/>
+      <c r="AL1" s="77"/>
+      <c r="AM1" s="77"/>
     </row>
     <row r="2" spans="1:39" s="59" customFormat="1">
       <c r="A2" s="63" t="s">
@@ -6712,94 +6716,94 @@
       <c r="E2" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="118" t="s">
+      <c r="F2" s="72" t="s">
         <v>1327</v>
       </c>
-      <c r="G2" s="118" t="s">
+      <c r="G2" s="72" t="s">
         <v>1328</v>
       </c>
-      <c r="H2" s="118" t="s">
+      <c r="H2" s="72" t="s">
         <v>1329</v>
       </c>
-      <c r="I2" s="118" t="s">
+      <c r="I2" s="72" t="s">
         <v>1330</v>
       </c>
-      <c r="J2" s="118" t="s">
+      <c r="J2" s="72" t="s">
         <v>1324</v>
       </c>
-      <c r="K2" s="118" t="s">
+      <c r="K2" s="72" t="s">
         <v>1325</v>
       </c>
-      <c r="L2" s="118" t="s">
+      <c r="L2" s="72" t="s">
         <v>1331</v>
       </c>
-      <c r="M2" s="118" t="s">
+      <c r="M2" s="72" t="s">
         <v>1332</v>
       </c>
-      <c r="N2" s="118" t="s">
+      <c r="N2" s="72" t="s">
         <v>1333</v>
       </c>
-      <c r="O2" s="118" t="s">
+      <c r="O2" s="72" t="s">
         <v>1334</v>
       </c>
-      <c r="P2" s="118" t="s">
+      <c r="P2" s="72" t="s">
         <v>1335</v>
       </c>
-      <c r="Q2" s="118" t="s">
+      <c r="Q2" s="72" t="s">
         <v>1336</v>
       </c>
-      <c r="R2" s="118" t="s">
+      <c r="R2" s="72" t="s">
         <v>1337</v>
       </c>
-      <c r="S2" s="118" t="s">
+      <c r="S2" s="72" t="s">
         <v>1338</v>
       </c>
-      <c r="T2" s="118" t="s">
+      <c r="T2" s="72" t="s">
         <v>1339</v>
       </c>
-      <c r="U2" s="118" t="s">
+      <c r="U2" s="72" t="s">
         <v>1340</v>
       </c>
-      <c r="V2" s="118" t="s">
+      <c r="V2" s="72" t="s">
         <v>1341</v>
       </c>
-      <c r="W2" s="118" t="s">
+      <c r="W2" s="72" t="s">
         <v>1342</v>
       </c>
-      <c r="X2" s="118" t="s">
+      <c r="X2" s="72" t="s">
         <v>1343</v>
       </c>
-      <c r="Y2" s="118" t="s">
+      <c r="Y2" s="72" t="s">
         <v>1344</v>
       </c>
-      <c r="Z2" s="118" t="s">
+      <c r="Z2" s="72" t="s">
         <v>1345</v>
       </c>
-      <c r="AA2" s="118" t="s">
+      <c r="AA2" s="72" t="s">
         <v>1346</v>
       </c>
-      <c r="AB2" s="118" t="s">
+      <c r="AB2" s="72" t="s">
         <v>1347</v>
       </c>
-      <c r="AC2" s="118" t="s">
+      <c r="AC2" s="72" t="s">
         <v>1348</v>
       </c>
-      <c r="AD2" s="118" t="s">
+      <c r="AD2" s="72" t="s">
         <v>1349</v>
       </c>
-      <c r="AE2" s="118" t="s">
+      <c r="AE2" s="72" t="s">
         <v>1350</v>
       </c>
-      <c r="AF2" s="118" t="s">
+      <c r="AF2" s="72" t="s">
         <v>1351</v>
       </c>
-      <c r="AG2" s="118" t="s">
+      <c r="AG2" s="72" t="s">
         <v>1352</v>
       </c>
-      <c r="AH2" s="118" t="s">
+      <c r="AH2" s="72" t="s">
         <v>1353</v>
       </c>
-      <c r="AI2" s="118" t="s">
+      <c r="AI2" s="72" t="s">
         <v>1354</v>
       </c>
       <c r="AJ2" s="65" t="s">
@@ -6813,6 +6817,17 @@
       </c>
       <c r="AM2" s="66" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39">
+      <c r="AK3" s="62" t="s">
+        <v>1247</v>
+      </c>
+      <c r="AL3" s="62" t="s">
+        <v>1260</v>
+      </c>
+      <c r="AM3" s="62" t="s">
+        <v>1261</v>
       </c>
     </row>
   </sheetData>
@@ -6822,7 +6837,7 @@
     <mergeCell ref="F1:AJ1"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
-  <dataValidations count="26">
+  <dataValidations count="27">
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="D2 AH3:AH65518"/>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过13位，小数位不可超过2位" sqref="I1:I2">
       <formula1>0</formula1>
@@ -6850,9 +6865,6 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2:C65504"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65504">
       <formula1>"01 银行间债券市场,02 商业银行柜台市场,03 上海证券交易所,04 深圳证券交易所,05 全国中小企业股份转让系统,06 上海期货交易所,07 郑州商品交易所,08 大连商品交易所,09 中国金融期货交易所,10 上海黄金交易所,11 区域性产权/资产交易市场,12 区域性商品交易所,13 区域性贵金属交易所,14 艺术品市场,15 基金市场,16 信托市场,17 全国银行间同业拆借市场,18 上海票据交易所,99 其他交易流通场所"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL3:AL1048576">
-      <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G65518">
       <formula1>"01 场内股票质押回购,02 场外股票质押融资,03 融资租赁,99 其他"</formula1>
@@ -6899,6 +6911,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z65518">
       <formula1>"01 房地产(保障房除外),02 地方政府融资平台,03 “铁公基”行业,04 “两高一剩”行业,99 其他"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL3:AL1048576">
+      <formula1>INDIRECT($AK$3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM3:AM1048576">
+      <formula1>INDIRECT($AL$3)</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <extLst>
@@ -6978,13 +6996,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="80"/>
+      <c r="B1" s="100"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="29" t="s">
@@ -6992,25 +7010,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="92"/>
+      <c r="A3" s="91"/>
       <c r="B3" s="26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="92"/>
+      <c r="A4" s="91"/>
       <c r="B4" s="26" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="93"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="24" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="17" customFormat="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="29" t="s">
@@ -7018,13 +7036,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="17" customFormat="1">
-      <c r="A7" s="95"/>
+      <c r="A7" s="94"/>
       <c r="B7" s="23" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="17" customFormat="1">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="95" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="22" t="s">
@@ -7032,13 +7050,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="17" customFormat="1">
-      <c r="A9" s="95"/>
+      <c r="A9" s="94"/>
       <c r="B9" s="23" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="96" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="26" t="s">
@@ -7114,7 +7132,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="96" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="29" t="s">
@@ -7128,13 +7146,13 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="85"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="24" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="96" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="26" t="s">
@@ -7196,13 +7214,13 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="85"/>
+      <c r="A35" s="98"/>
       <c r="B35" s="41" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="96" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="21" t="s">
@@ -7222,13 +7240,13 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="85"/>
+      <c r="A39" s="98"/>
       <c r="B39" s="21" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="84" t="s">
+      <c r="A40" s="96" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="20" t="s">
@@ -7266,13 +7284,13 @@
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="85"/>
+      <c r="A46" s="98"/>
       <c r="B46" s="24" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="84" t="s">
+      <c r="A47" s="96" t="s">
         <v>84</v>
       </c>
       <c r="B47" s="29" t="s">
@@ -7328,13 +7346,13 @@
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="85"/>
+      <c r="A56" s="98"/>
       <c r="B56" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="84" t="s">
+      <c r="A57" s="96" t="s">
         <v>95</v>
       </c>
       <c r="B57" s="20" t="s">
@@ -7348,13 +7366,13 @@
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="85"/>
+      <c r="A59" s="98"/>
       <c r="B59" s="24" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="96" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="34" t="s">
@@ -7386,13 +7404,13 @@
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="85"/>
+      <c r="A65" s="98"/>
       <c r="B65" s="28" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="84" t="s">
+      <c r="A66" s="96" t="s">
         <v>106</v>
       </c>
       <c r="B66" s="34" t="s">
@@ -7424,13 +7442,13 @@
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="85"/>
+      <c r="A71" s="98"/>
       <c r="B71" s="28" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="17" customFormat="1">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="96" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="21" t="s">
@@ -7528,13 +7546,13 @@
       </c>
     </row>
     <row r="88" spans="1:6" s="17" customFormat="1">
-      <c r="A88" s="85"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="17" customFormat="1">
-      <c r="A89" s="84" t="s">
+      <c r="A89" s="96" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="26" t="s">
@@ -7567,13 +7585,13 @@
       </c>
     </row>
     <row r="94" spans="1:6" s="17" customFormat="1">
-      <c r="A94" s="85"/>
+      <c r="A94" s="98"/>
       <c r="B94" s="24" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="17" customFormat="1">
-      <c r="A95" s="84" t="s">
+      <c r="A95" s="96" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="37" t="s">
@@ -7611,13 +7629,13 @@
       </c>
     </row>
     <row r="101" spans="1:2" s="17" customFormat="1">
-      <c r="A101" s="85"/>
+      <c r="A101" s="98"/>
       <c r="B101" s="32" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="17" customFormat="1">
-      <c r="A102" s="84" t="s">
+      <c r="A102" s="96" t="s">
         <v>146</v>
       </c>
       <c r="B102" s="20" t="s">
@@ -7625,7 +7643,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="17" customFormat="1">
-      <c r="A103" s="85"/>
+      <c r="A103" s="98"/>
       <c r="B103" s="24" t="s">
         <v>148</v>
       </c>
@@ -7643,10 +7661,10 @@
       <c r="B105" s="27"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="79" t="s">
+      <c r="A107" s="99" t="s">
         <v>151</v>
       </c>
-      <c r="B107" s="80"/>
+      <c r="B107" s="100"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="47"/>
@@ -7817,17 +7835,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="98" t="s">
+      <c r="A137" s="84" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="99"/>
+      <c r="B137" s="85"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="100"/>
-      <c r="B138" s="101"/>
+      <c r="A138" s="86"/>
+      <c r="B138" s="87"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="86" t="s">
+      <c r="A139" s="81" t="s">
         <v>181</v>
       </c>
       <c r="B139" s="49" t="s">
@@ -7835,31 +7853,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="87"/>
+      <c r="A140" s="82"/>
       <c r="B140" s="50" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="87"/>
+      <c r="A141" s="82"/>
       <c r="B141" s="50" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="87"/>
+      <c r="A142" s="82"/>
       <c r="B142" s="50" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="88"/>
+      <c r="A143" s="83"/>
       <c r="B143" s="52" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="86" t="s">
+      <c r="A144" s="81" t="s">
         <v>187</v>
       </c>
       <c r="B144" s="49" t="s">
@@ -7867,43 +7885,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="87"/>
+      <c r="A145" s="82"/>
       <c r="B145" s="50" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="87"/>
+      <c r="A146" s="82"/>
       <c r="B146" s="50" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="87"/>
+      <c r="A147" s="82"/>
       <c r="B147" s="50" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="87"/>
+      <c r="A148" s="82"/>
       <c r="B148" s="50" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="87"/>
+      <c r="A149" s="82"/>
       <c r="B149" s="50" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="88"/>
+      <c r="A150" s="83"/>
       <c r="B150" s="52" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="86" t="s">
+      <c r="A151" s="81" t="s">
         <v>195</v>
       </c>
       <c r="B151" s="49" t="s">
@@ -7911,187 +7929,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="87"/>
+      <c r="A152" s="82"/>
       <c r="B152" s="50" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="87"/>
+      <c r="A153" s="82"/>
       <c r="B153" s="50" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="87"/>
+      <c r="A154" s="82"/>
       <c r="B154" s="50" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="87"/>
+      <c r="A155" s="82"/>
       <c r="B155" s="50" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="87"/>
+      <c r="A156" s="82"/>
       <c r="B156" s="50" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="87"/>
+      <c r="A157" s="82"/>
       <c r="B157" s="50" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="87"/>
+      <c r="A158" s="82"/>
       <c r="B158" s="50" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="87"/>
+      <c r="A159" s="82"/>
       <c r="B159" s="50" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="87"/>
+      <c r="A160" s="82"/>
       <c r="B160" s="50" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="87"/>
+      <c r="A161" s="82"/>
       <c r="B161" s="50" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="87"/>
+      <c r="A162" s="82"/>
       <c r="B162" s="50" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="87"/>
+      <c r="A163" s="82"/>
       <c r="B163" s="50" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="87"/>
+      <c r="A164" s="82"/>
       <c r="B164" s="50" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="87"/>
+      <c r="A165" s="82"/>
       <c r="B165" s="50" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="87"/>
+      <c r="A166" s="82"/>
       <c r="B166" s="50" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="87"/>
+      <c r="A167" s="82"/>
       <c r="B167" s="50" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="87"/>
+      <c r="A168" s="82"/>
       <c r="B168" s="50" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="87"/>
+      <c r="A169" s="82"/>
       <c r="B169" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="87"/>
+      <c r="A170" s="82"/>
       <c r="B170" s="50" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="87"/>
+      <c r="A171" s="82"/>
       <c r="B171" s="50" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="87"/>
+      <c r="A172" s="82"/>
       <c r="B172" s="50" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="87"/>
+      <c r="A173" s="82"/>
       <c r="B173" s="50" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="87"/>
+      <c r="A174" s="82"/>
       <c r="B174" s="50" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="87"/>
+      <c r="A175" s="82"/>
       <c r="B175" s="50" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="87"/>
+      <c r="A176" s="82"/>
       <c r="B176" s="50" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="87"/>
+      <c r="A177" s="82"/>
       <c r="B177" s="50" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="87"/>
+      <c r="A178" s="82"/>
       <c r="B178" s="50" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="87"/>
+      <c r="A179" s="82"/>
       <c r="B179" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="87"/>
+      <c r="A180" s="82"/>
       <c r="B180" s="50" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="88"/>
+      <c r="A181" s="83"/>
       <c r="B181" s="52" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="86" t="s">
+      <c r="A182" s="81" t="s">
         <v>227</v>
       </c>
       <c r="B182" s="49" t="s">
@@ -8099,19 +8117,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="87"/>
+      <c r="A183" s="82"/>
       <c r="B183" s="50" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="88"/>
+      <c r="A184" s="83"/>
       <c r="B184" s="52" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="86" t="s">
+      <c r="A185" s="81" t="s">
         <v>231</v>
       </c>
       <c r="B185" s="49" t="s">
@@ -8119,25 +8137,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="87"/>
+      <c r="A186" s="82"/>
       <c r="B186" s="50" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="87"/>
+      <c r="A187" s="82"/>
       <c r="B187" s="50" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="88"/>
+      <c r="A188" s="83"/>
       <c r="B188" s="52" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="86" t="s">
+      <c r="A189" s="81" t="s">
         <v>236</v>
       </c>
       <c r="B189" s="49" t="s">
@@ -8145,13 +8163,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="88"/>
+      <c r="A190" s="83"/>
       <c r="B190" s="52" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="86" t="s">
+      <c r="A191" s="81" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="49" t="s">
@@ -8159,49 +8177,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="87"/>
+      <c r="A192" s="82"/>
       <c r="B192" s="50" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="87"/>
+      <c r="A193" s="82"/>
       <c r="B193" s="50" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="87"/>
+      <c r="A194" s="82"/>
       <c r="B194" s="50" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="87"/>
+      <c r="A195" s="82"/>
       <c r="B195" s="50" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="87"/>
+      <c r="A196" s="82"/>
       <c r="B196" s="50" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="87"/>
+      <c r="A197" s="82"/>
       <c r="B197" s="50" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="88"/>
+      <c r="A198" s="83"/>
       <c r="B198" s="52" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="86" t="s">
+      <c r="A199" s="81" t="s">
         <v>248</v>
       </c>
       <c r="B199" s="49" t="s">
@@ -8209,13 +8227,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="88"/>
+      <c r="A200" s="83"/>
       <c r="B200" s="52" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="86" t="s">
+      <c r="A201" s="81" t="s">
         <v>251</v>
       </c>
       <c r="B201" s="49" t="s">
@@ -8223,19 +8241,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="87"/>
+      <c r="A202" s="82"/>
       <c r="B202" s="50" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="88"/>
+      <c r="A203" s="83"/>
       <c r="B203" s="52" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="86" t="s">
+      <c r="A204" s="81" t="s">
         <v>255</v>
       </c>
       <c r="B204" s="49" t="s">
@@ -8243,19 +8261,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="87"/>
+      <c r="A205" s="82"/>
       <c r="B205" s="50" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="87"/>
+      <c r="A206" s="82"/>
       <c r="B206" s="50" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="88"/>
+      <c r="A207" s="83"/>
       <c r="B207" s="52" t="s">
         <v>259</v>
       </c>
@@ -8269,7 +8287,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="86" t="s">
+      <c r="A209" s="81" t="s">
         <v>262</v>
       </c>
       <c r="B209" s="49" t="s">
@@ -8277,13 +8295,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="88"/>
+      <c r="A210" s="83"/>
       <c r="B210" s="52" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="86" t="s">
+      <c r="A211" s="81" t="s">
         <v>265</v>
       </c>
       <c r="B211" s="49" t="s">
@@ -8291,19 +8309,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="87"/>
+      <c r="A212" s="82"/>
       <c r="B212" s="50" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="88"/>
+      <c r="A213" s="83"/>
       <c r="B213" s="52" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="86" t="s">
+      <c r="A214" s="81" t="s">
         <v>269</v>
       </c>
       <c r="B214" s="49" t="s">
@@ -8311,19 +8329,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="87"/>
+      <c r="A215" s="82"/>
       <c r="B215" s="50" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="88"/>
+      <c r="A216" s="83"/>
       <c r="B216" s="52" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="86" t="s">
+      <c r="A217" s="81" t="s">
         <v>273</v>
       </c>
       <c r="B217" s="49" t="s">
@@ -8331,13 +8349,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="87"/>
+      <c r="A218" s="82"/>
       <c r="B218" s="50" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="88"/>
+      <c r="A219" s="83"/>
       <c r="B219" s="52" t="s">
         <v>276</v>
       </c>
@@ -8351,7 +8369,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="86" t="s">
+      <c r="A221" s="81" t="s">
         <v>279</v>
       </c>
       <c r="B221" s="49" t="s">
@@ -8359,13 +8377,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="88"/>
+      <c r="A222" s="83"/>
       <c r="B222" s="52" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="86" t="s">
+      <c r="A223" s="81" t="s">
         <v>282</v>
       </c>
       <c r="B223" s="49" t="s">
@@ -8373,31 +8391,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="87"/>
+      <c r="A224" s="82"/>
       <c r="B224" s="50" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="87"/>
+      <c r="A225" s="82"/>
       <c r="B225" s="50" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="87"/>
+      <c r="A226" s="82"/>
       <c r="B226" s="50" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="88"/>
+      <c r="A227" s="83"/>
       <c r="B227" s="52" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="86" t="s">
+      <c r="A228" s="81" t="s">
         <v>288</v>
       </c>
       <c r="B228" s="49" t="s">
@@ -8405,31 +8423,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="87"/>
+      <c r="A229" s="82"/>
       <c r="B229" s="50" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="87"/>
+      <c r="A230" s="82"/>
       <c r="B230" s="50" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="87"/>
+      <c r="A231" s="82"/>
       <c r="B231" s="50" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="87"/>
+      <c r="A232" s="82"/>
       <c r="B232" s="50" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="88"/>
+      <c r="A233" s="83"/>
       <c r="B233" s="52" t="s">
         <v>294</v>
       </c>
@@ -8443,16 +8461,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="81" t="s">
+      <c r="A236" s="101" t="s">
         <v>297</v>
       </c>
-      <c r="B236" s="80"/>
+      <c r="B236" s="100"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="79" t="s">
+      <c r="A239" s="99" t="s">
         <v>298</v>
       </c>
-      <c r="B239" s="80"/>
+      <c r="B239" s="100"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="47"/>
@@ -8551,10 +8569,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="82" t="s">
+      <c r="A257" s="102" t="s">
         <v>315</v>
       </c>
-      <c r="B257" s="83"/>
+      <c r="B257" s="103"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="47"/>
@@ -8731,10 +8749,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="89" t="s">
+      <c r="A288" s="88" t="s">
         <v>345</v>
       </c>
-      <c r="B288" s="90"/>
+      <c r="B288" s="89"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="55"/>
@@ -8925,14 +8943,22 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -8949,22 +8975,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8984,10 +9002,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="113" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="103"/>
+      <c r="B1" s="114"/>
     </row>
     <row r="2" spans="1:2" s="15" customFormat="1" ht="14.25">
       <c r="A2" s="18" t="s">
@@ -9001,7 +9019,7 @@
       <c r="A3" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="107" t="s">
         <v>1</v>
       </c>
     </row>
@@ -9009,25 +9027,25 @@
       <c r="A4" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="105"/>
+      <c r="B4" s="108"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="105"/>
+      <c r="B5" s="108"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="106"/>
+      <c r="B6" s="109"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="107" t="s">
         <v>382</v>
       </c>
     </row>
@@ -9035,25 +9053,25 @@
       <c r="A8" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="105"/>
+      <c r="B8" s="108"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="105"/>
+      <c r="B9" s="108"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="106"/>
+      <c r="B10" s="109"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="107" t="s">
         <v>2</v>
       </c>
     </row>
@@ -9061,85 +9079,85 @@
       <c r="A12" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="105"/>
+      <c r="B12" s="108"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="105"/>
+      <c r="B13" s="108"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="105"/>
+      <c r="B14" s="108"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="105"/>
+      <c r="B15" s="108"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="105"/>
+      <c r="B16" s="108"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="105"/>
+      <c r="B17" s="108"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="105"/>
+      <c r="B18" s="108"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="105"/>
+      <c r="B19" s="108"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="105"/>
+      <c r="B20" s="108"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="26" t="s">
         <v>385</v>
       </c>
-      <c r="B21" s="105"/>
+      <c r="B21" s="108"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="105"/>
+      <c r="B22" s="108"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="107"/>
+      <c r="B23" s="115"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="108"/>
+      <c r="B24" s="116"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="104" t="s">
+      <c r="B25" s="107" t="s">
         <v>3</v>
       </c>
     </row>
@@ -9147,61 +9165,61 @@
       <c r="A26" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="105"/>
+      <c r="B26" s="108"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="105"/>
+      <c r="B27" s="108"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="105"/>
+      <c r="B28" s="108"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="105"/>
+      <c r="B29" s="108"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="105"/>
+      <c r="B30" s="108"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="105"/>
+      <c r="B31" s="108"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="105"/>
+      <c r="B32" s="108"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="105"/>
+      <c r="B33" s="108"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="106"/>
+      <c r="B34" s="109"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="29" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="104" t="s">
+      <c r="B35" s="107" t="s">
         <v>391</v>
       </c>
     </row>
@@ -9209,13 +9227,13 @@
       <c r="A36" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="106"/>
+      <c r="B36" s="109"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="104" t="s">
+      <c r="B37" s="107" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9223,19 +9241,19 @@
       <c r="A38" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="105"/>
+      <c r="B38" s="108"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="105"/>
+      <c r="B39" s="108"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="104" t="s">
+      <c r="B40" s="107" t="s">
         <v>394</v>
       </c>
     </row>
@@ -9243,37 +9261,37 @@
       <c r="A41" s="21" t="s">
         <v>395</v>
       </c>
-      <c r="B41" s="105"/>
+      <c r="B41" s="108"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="105"/>
+      <c r="B42" s="108"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="B43" s="105"/>
+      <c r="B43" s="108"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="21" t="s">
         <v>397</v>
       </c>
-      <c r="B44" s="105"/>
+      <c r="B44" s="108"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="105"/>
+      <c r="B45" s="108"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="106"/>
+      <c r="B46" s="109"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="30" t="s">
@@ -9287,7 +9305,7 @@
       <c r="A48" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="104" t="s">
+      <c r="B48" s="107" t="s">
         <v>398</v>
       </c>
     </row>
@@ -9295,13 +9313,13 @@
       <c r="A49" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="106"/>
+      <c r="B49" s="109"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="104" t="s">
+      <c r="B50" s="107" t="s">
         <v>6</v>
       </c>
     </row>
@@ -9309,25 +9327,25 @@
       <c r="A51" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="105"/>
+      <c r="B51" s="108"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="105"/>
+      <c r="B52" s="108"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="105"/>
+      <c r="B53" s="108"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="106"/>
+      <c r="B54" s="109"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="30" t="s">
@@ -9341,7 +9359,7 @@
       <c r="A56" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="104" t="s">
+      <c r="B56" s="107" t="s">
         <v>8</v>
       </c>
     </row>
@@ -9349,19 +9367,19 @@
       <c r="A57" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B57" s="105"/>
+      <c r="B57" s="108"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="106"/>
+      <c r="B58" s="109"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="104" t="s">
+      <c r="B59" s="107" t="s">
         <v>7</v>
       </c>
     </row>
@@ -9369,37 +9387,37 @@
       <c r="A60" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="105"/>
+      <c r="B60" s="108"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="105"/>
+      <c r="B61" s="108"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="105"/>
+      <c r="B62" s="108"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="105"/>
+      <c r="B63" s="108"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="106"/>
+      <c r="B64" s="109"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="21" t="s">
         <v>401</v>
       </c>
-      <c r="B65" s="112" t="s">
+      <c r="B65" s="110" t="s">
         <v>402</v>
       </c>
     </row>
@@ -9407,26 +9425,26 @@
       <c r="A66" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="113"/>
+      <c r="B66" s="111"/>
       <c r="E66" s="33"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="113"/>
+      <c r="B67" s="111"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="114"/>
+      <c r="B68" s="112"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="104" t="s">
+      <c r="B69" s="107" t="s">
         <v>9</v>
       </c>
     </row>
@@ -9434,37 +9452,37 @@
       <c r="A70" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="105"/>
+      <c r="B70" s="108"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="105"/>
+      <c r="B71" s="108"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="105"/>
+      <c r="B72" s="108"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B73" s="105"/>
+      <c r="B73" s="108"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="106"/>
+      <c r="B74" s="109"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="104" t="s">
+      <c r="B75" s="107" t="s">
         <v>10</v>
       </c>
     </row>
@@ -9472,139 +9490,139 @@
       <c r="A76" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="105"/>
+      <c r="B76" s="108"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="105"/>
+      <c r="B77" s="108"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="105"/>
+      <c r="B78" s="108"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="105"/>
+      <c r="B79" s="108"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="105"/>
+      <c r="B80" s="108"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="105"/>
+      <c r="B81" s="108"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B82" s="105"/>
+      <c r="B82" s="108"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="105"/>
+      <c r="B83" s="108"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B84" s="105"/>
+      <c r="B84" s="108"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="105"/>
+      <c r="B85" s="108"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="105"/>
+      <c r="B86" s="108"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="105"/>
+      <c r="B87" s="108"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="105"/>
+      <c r="B88" s="108"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="105"/>
+      <c r="B89" s="108"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="105"/>
+      <c r="B90" s="108"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="105"/>
+      <c r="B91" s="108"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="105"/>
+      <c r="B92" s="108"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="105"/>
+      <c r="B93" s="108"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="105"/>
+      <c r="B94" s="108"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="105"/>
+      <c r="B95" s="108"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="105"/>
+      <c r="B96" s="108"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B97" s="105"/>
+      <c r="B97" s="108"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="109" t="s">
+      <c r="B98" s="104" t="s">
         <v>11</v>
       </c>
     </row>
@@ -9612,37 +9630,37 @@
       <c r="A99" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="110"/>
+      <c r="B99" s="105"/>
     </row>
     <row r="100" spans="1:2" s="16" customFormat="1">
       <c r="A100" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="110"/>
+      <c r="B100" s="105"/>
     </row>
     <row r="101" spans="1:2" s="16" customFormat="1">
       <c r="A101" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="110"/>
+      <c r="B101" s="105"/>
     </row>
     <row r="102" spans="1:2" s="16" customFormat="1">
       <c r="A102" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="110"/>
+      <c r="B102" s="105"/>
     </row>
     <row r="103" spans="1:2" s="16" customFormat="1">
       <c r="A103" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="110"/>
+      <c r="B103" s="105"/>
     </row>
     <row r="104" spans="1:2" s="16" customFormat="1">
       <c r="A104" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="111"/>
+      <c r="B104" s="106"/>
     </row>
     <row r="105" spans="1:2" s="16" customFormat="1">
       <c r="A105" s="38" t="s">
@@ -9654,22 +9672,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -9712,10 +9730,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27" customHeight="1">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="117" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="116"/>
+      <c r="B1" s="118"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="11" t="s">
@@ -11651,10 +11669,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="119" t="s">
         <v>884</v>
       </c>
-      <c r="B1" s="117"/>
+      <c r="B1" s="119"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
@@ -13095,6 +13113,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.625" customWidth="1"/>
     <col min="14" max="14" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13285,11 +13304,11 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" t="s">
-        <v>1259</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1259</v>
+      <c r="A17" s="68" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B17" s="68" t="s">
+        <v>1355</v>
       </c>
     </row>
     <row r="18" spans="1:16">

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepOtherInvestTargetInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepOtherInvestTargetInfo.xlsx
@@ -4743,27 +4743,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4771,6 +4750,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4797,40 +4788,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4843,6 +4822,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4850,6 +4838,18 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5414,7 +5414,7 @@
     <mergeCell ref="F1:AJ1"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
-  <dataValidations count="27">
+  <dataValidations count="26">
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="D2 AH3:AH65518"/>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过13位，小数位不可超过2位" sqref="I1:I2">
       <formula1>0</formula1>
@@ -5439,7 +5439,6 @@
       <formula1>-999.99999</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65504">
       <formula1>"01 银行间债券市场,02 商业银行柜台市场,03 上海证券交易所,04 深圳证券交易所,05 全国中小企业股份转让系统,06 上海期货交易所,07 郑州商品交易所,08 大连商品交易所,09 中国金融期货交易所,10 上海黄金交易所,11 区域性产权/资产交易市场,12 区域性商品交易所,13 区域性贵金属交易所,14 艺术品市场,15 基金市场,16 信托市场,17 全国银行间同业拆借市场,18 上海票据交易所,99 其他交易流通场所"</formula1>
     </dataValidation>
@@ -5511,9 +5510,9 @@
           </x14:formula1>
           <xm:sqref>E1 E3:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>各类资产应填要素列说明!$A$25:$A$34</xm:f>
+            <xm:f>各类资产应填要素列说明!$A$65:$A$68</xm:f>
           </x14:formula1>
           <xm:sqref>C1 C3:C1048576</xm:sqref>
         </x14:dataValidation>
@@ -5585,13 +5584,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="71"/>
+      <c r="B1" s="89"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="79" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5599,25 +5598,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="83"/>
+      <c r="A3" s="80"/>
       <c r="B3" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="83"/>
+      <c r="A4" s="80"/>
       <c r="B4" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="84"/>
+      <c r="A5" s="81"/>
       <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5625,13 +5624,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="86"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="84" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5639,13 +5638,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="86"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="75" t="s">
+      <c r="A10" s="85" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5653,61 +5652,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="88"/>
+      <c r="A11" s="86"/>
       <c r="B11" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="88"/>
+      <c r="A12" s="86"/>
       <c r="B12" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="88"/>
+      <c r="A13" s="86"/>
       <c r="B13" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="88"/>
+      <c r="A14" s="86"/>
       <c r="B14" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="88"/>
+      <c r="A15" s="86"/>
       <c r="B15" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="88"/>
+      <c r="A16" s="86"/>
       <c r="B16" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="88"/>
+      <c r="A17" s="86"/>
       <c r="B17" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="88"/>
+      <c r="A18" s="86"/>
       <c r="B18" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="88"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="88"/>
+      <c r="A20" s="86"/>
       <c r="B20" s="15" t="s">
         <v>52</v>
       </c>
@@ -5721,7 +5720,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -5729,19 +5728,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="88"/>
+      <c r="A23" s="86"/>
       <c r="B23" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="76"/>
+      <c r="A24" s="87"/>
       <c r="B24" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="75" t="s">
+      <c r="A25" s="85" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -5749,67 +5748,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="88"/>
+      <c r="A26" s="86"/>
       <c r="B26" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="88"/>
+      <c r="A27" s="86"/>
       <c r="B27" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="88"/>
+      <c r="A28" s="86"/>
       <c r="B28" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="88"/>
+      <c r="A29" s="86"/>
       <c r="B29" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="88"/>
+      <c r="A30" s="86"/>
       <c r="B30" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="88"/>
+      <c r="A31" s="86"/>
       <c r="B31" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="88"/>
+      <c r="A32" s="86"/>
       <c r="B32" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="88"/>
+      <c r="A33" s="86"/>
       <c r="B33" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="88"/>
+      <c r="A34" s="86"/>
       <c r="B34" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="76"/>
+      <c r="A35" s="87"/>
       <c r="B35" s="30" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="75" t="s">
+      <c r="A36" s="85" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -5817,25 +5816,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="88"/>
+      <c r="A37" s="86"/>
       <c r="B37" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="88"/>
+      <c r="A38" s="86"/>
       <c r="B38" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="76"/>
+      <c r="A39" s="87"/>
       <c r="B39" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="75" t="s">
+      <c r="A40" s="85" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -5843,43 +5842,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="88"/>
+      <c r="A41" s="86"/>
       <c r="B41" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="88"/>
+      <c r="A42" s="86"/>
       <c r="B42" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="88"/>
+      <c r="A43" s="86"/>
       <c r="B43" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="88"/>
+      <c r="A44" s="86"/>
       <c r="B44" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="88"/>
+      <c r="A45" s="86"/>
       <c r="B45" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="76"/>
+      <c r="A46" s="87"/>
       <c r="B46" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="75" t="s">
+      <c r="A47" s="85" t="s">
         <v>84</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -5887,61 +5886,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="88"/>
+      <c r="A48" s="86"/>
       <c r="B48" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="88"/>
+      <c r="A49" s="86"/>
       <c r="B49" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="88"/>
+      <c r="A50" s="86"/>
       <c r="B50" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="88"/>
+      <c r="A51" s="86"/>
       <c r="B51" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="88"/>
+      <c r="A52" s="86"/>
       <c r="B52" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="88"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="88"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="88"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="76"/>
+      <c r="A56" s="87"/>
       <c r="B56" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="75" t="s">
+      <c r="A57" s="85" t="s">
         <v>95</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -5949,19 +5948,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="88"/>
+      <c r="A58" s="86"/>
       <c r="B58" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="76"/>
+      <c r="A59" s="87"/>
       <c r="B59" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="75" t="s">
+      <c r="A60" s="85" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -5969,37 +5968,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="88"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="88"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="24" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="88"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="88"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="76"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="17" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="75" t="s">
+      <c r="A66" s="85" t="s">
         <v>106</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -6007,37 +6006,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="88"/>
+      <c r="A67" s="86"/>
       <c r="B67" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="88"/>
+      <c r="A68" s="86"/>
       <c r="B68" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="88"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="88"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="76"/>
+      <c r="A71" s="87"/>
       <c r="B71" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="75" t="s">
+      <c r="A72" s="85" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -6045,103 +6044,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="88"/>
+      <c r="A73" s="86"/>
       <c r="B73" s="10" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="88"/>
+      <c r="A74" s="86"/>
       <c r="B74" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="88"/>
+      <c r="A75" s="86"/>
       <c r="B75" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="88"/>
+      <c r="A76" s="86"/>
       <c r="B76" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="88"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="25" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="88"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="10" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="88"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="88"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="88"/>
+      <c r="A81" s="86"/>
       <c r="B81" s="25" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="88"/>
+      <c r="A82" s="86"/>
       <c r="B82" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="88"/>
+      <c r="A83" s="86"/>
       <c r="B83" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="88"/>
+      <c r="A84" s="86"/>
       <c r="B84" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="88"/>
+      <c r="A85" s="86"/>
       <c r="B85" s="25" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="88"/>
+      <c r="A86" s="86"/>
       <c r="B86" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="88"/>
+      <c r="A87" s="86"/>
       <c r="B87" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="76"/>
+      <c r="A88" s="87"/>
       <c r="B88" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="75" t="s">
+      <c r="A89" s="85" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -6149,38 +6148,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="88"/>
+      <c r="A90" s="86"/>
       <c r="B90" s="15" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="88"/>
+      <c r="A91" s="86"/>
       <c r="B91" s="15" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="88"/>
+      <c r="A92" s="86"/>
       <c r="B92" s="32" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="88"/>
+      <c r="A93" s="86"/>
       <c r="B93" s="15" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="76"/>
+      <c r="A94" s="87"/>
       <c r="B94" s="13" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="75" t="s">
+      <c r="A95" s="85" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -6188,43 +6187,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="88"/>
+      <c r="A96" s="86"/>
       <c r="B96" s="25" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="88"/>
+      <c r="A97" s="86"/>
       <c r="B97" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="88"/>
+      <c r="A98" s="86"/>
       <c r="B98" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="88"/>
+      <c r="A99" s="86"/>
       <c r="B99" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="88"/>
+      <c r="A100" s="86"/>
       <c r="B100" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="76"/>
+      <c r="A101" s="87"/>
       <c r="B101" s="21" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="75" t="s">
+      <c r="A102" s="85" t="s">
         <v>146</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -6232,7 +6231,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="76"/>
+      <c r="A103" s="87"/>
       <c r="B103" s="13" t="s">
         <v>148</v>
       </c>
@@ -6250,10 +6249,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="70" t="s">
+      <c r="A107" s="88" t="s">
         <v>151</v>
       </c>
-      <c r="B107" s="71"/>
+      <c r="B107" s="89"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6424,17 +6423,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="89" t="s">
+      <c r="A137" s="73" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="90"/>
+      <c r="B137" s="74"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="91"/>
-      <c r="B138" s="92"/>
+      <c r="A138" s="75"/>
+      <c r="B138" s="76"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="77" t="s">
+      <c r="A139" s="70" t="s">
         <v>181</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6442,31 +6441,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="78"/>
+      <c r="A140" s="71"/>
       <c r="B140" s="39" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="78"/>
+      <c r="A141" s="71"/>
       <c r="B141" s="39" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="78"/>
+      <c r="A142" s="71"/>
       <c r="B142" s="39" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="79"/>
+      <c r="A143" s="72"/>
       <c r="B143" s="41" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="77" t="s">
+      <c r="A144" s="70" t="s">
         <v>187</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6474,43 +6473,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="78"/>
+      <c r="A145" s="71"/>
       <c r="B145" s="39" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="78"/>
+      <c r="A146" s="71"/>
       <c r="B146" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="78"/>
+      <c r="A147" s="71"/>
       <c r="B147" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="78"/>
+      <c r="A148" s="71"/>
       <c r="B148" s="39" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="78"/>
+      <c r="A149" s="71"/>
       <c r="B149" s="39" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="79"/>
+      <c r="A150" s="72"/>
       <c r="B150" s="41" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="77" t="s">
+      <c r="A151" s="70" t="s">
         <v>195</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6518,187 +6517,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="78"/>
+      <c r="A152" s="71"/>
       <c r="B152" s="39" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="78"/>
+      <c r="A153" s="71"/>
       <c r="B153" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="78"/>
+      <c r="A154" s="71"/>
       <c r="B154" s="39" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="78"/>
+      <c r="A155" s="71"/>
       <c r="B155" s="39" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="78"/>
+      <c r="A156" s="71"/>
       <c r="B156" s="39" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="78"/>
+      <c r="A157" s="71"/>
       <c r="B157" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="78"/>
+      <c r="A158" s="71"/>
       <c r="B158" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="78"/>
+      <c r="A159" s="71"/>
       <c r="B159" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="78"/>
+      <c r="A160" s="71"/>
       <c r="B160" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="78"/>
+      <c r="A161" s="71"/>
       <c r="B161" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="78"/>
+      <c r="A162" s="71"/>
       <c r="B162" s="39" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="78"/>
+      <c r="A163" s="71"/>
       <c r="B163" s="39" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="78"/>
+      <c r="A164" s="71"/>
       <c r="B164" s="39" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="78"/>
+      <c r="A165" s="71"/>
       <c r="B165" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="78"/>
+      <c r="A166" s="71"/>
       <c r="B166" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="78"/>
+      <c r="A167" s="71"/>
       <c r="B167" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="78"/>
+      <c r="A168" s="71"/>
       <c r="B168" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="78"/>
+      <c r="A169" s="71"/>
       <c r="B169" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="78"/>
+      <c r="A170" s="71"/>
       <c r="B170" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="78"/>
+      <c r="A171" s="71"/>
       <c r="B171" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="78"/>
+      <c r="A172" s="71"/>
       <c r="B172" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="78"/>
+      <c r="A173" s="71"/>
       <c r="B173" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="78"/>
+      <c r="A174" s="71"/>
       <c r="B174" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="78"/>
+      <c r="A175" s="71"/>
       <c r="B175" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="78"/>
+      <c r="A176" s="71"/>
       <c r="B176" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="78"/>
+      <c r="A177" s="71"/>
       <c r="B177" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="78"/>
+      <c r="A178" s="71"/>
       <c r="B178" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="78"/>
+      <c r="A179" s="71"/>
       <c r="B179" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="78"/>
+      <c r="A180" s="71"/>
       <c r="B180" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="79"/>
+      <c r="A181" s="72"/>
       <c r="B181" s="41" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="77" t="s">
+      <c r="A182" s="70" t="s">
         <v>227</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6706,19 +6705,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="78"/>
+      <c r="A183" s="71"/>
       <c r="B183" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="79"/>
+      <c r="A184" s="72"/>
       <c r="B184" s="41" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="77" t="s">
+      <c r="A185" s="70" t="s">
         <v>231</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6726,25 +6725,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="78"/>
+      <c r="A186" s="71"/>
       <c r="B186" s="39" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="78"/>
+      <c r="A187" s="71"/>
       <c r="B187" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="79"/>
+      <c r="A188" s="72"/>
       <c r="B188" s="41" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="77" t="s">
+      <c r="A189" s="70" t="s">
         <v>236</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -6752,13 +6751,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="79"/>
+      <c r="A190" s="72"/>
       <c r="B190" s="41" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="77" t="s">
+      <c r="A191" s="70" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -6766,49 +6765,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="78"/>
+      <c r="A192" s="71"/>
       <c r="B192" s="39" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="78"/>
+      <c r="A193" s="71"/>
       <c r="B193" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="78"/>
+      <c r="A194" s="71"/>
       <c r="B194" s="39" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="78"/>
+      <c r="A195" s="71"/>
       <c r="B195" s="39" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="78"/>
+      <c r="A196" s="71"/>
       <c r="B196" s="39" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="78"/>
+      <c r="A197" s="71"/>
       <c r="B197" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="79"/>
+      <c r="A198" s="72"/>
       <c r="B198" s="41" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="77" t="s">
+      <c r="A199" s="70" t="s">
         <v>248</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -6816,13 +6815,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="79"/>
+      <c r="A200" s="72"/>
       <c r="B200" s="41" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="77" t="s">
+      <c r="A201" s="70" t="s">
         <v>251</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -6830,19 +6829,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="78"/>
+      <c r="A202" s="71"/>
       <c r="B202" s="39" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="79"/>
+      <c r="A203" s="72"/>
       <c r="B203" s="41" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="77" t="s">
+      <c r="A204" s="70" t="s">
         <v>255</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -6850,19 +6849,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="78"/>
+      <c r="A205" s="71"/>
       <c r="B205" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="78"/>
+      <c r="A206" s="71"/>
       <c r="B206" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="79"/>
+      <c r="A207" s="72"/>
       <c r="B207" s="41" t="s">
         <v>259</v>
       </c>
@@ -6876,7 +6875,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="77" t="s">
+      <c r="A209" s="70" t="s">
         <v>262</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -6884,13 +6883,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="79"/>
+      <c r="A210" s="72"/>
       <c r="B210" s="41" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="77" t="s">
+      <c r="A211" s="70" t="s">
         <v>265</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -6898,19 +6897,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="78"/>
+      <c r="A212" s="71"/>
       <c r="B212" s="39" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="79"/>
+      <c r="A213" s="72"/>
       <c r="B213" s="41" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="77" t="s">
+      <c r="A214" s="70" t="s">
         <v>269</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -6918,19 +6917,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="78"/>
+      <c r="A215" s="71"/>
       <c r="B215" s="39" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="79"/>
+      <c r="A216" s="72"/>
       <c r="B216" s="41" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="77" t="s">
+      <c r="A217" s="70" t="s">
         <v>273</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -6938,13 +6937,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="78"/>
+      <c r="A218" s="71"/>
       <c r="B218" s="39" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="79"/>
+      <c r="A219" s="72"/>
       <c r="B219" s="41" t="s">
         <v>276</v>
       </c>
@@ -6958,7 +6957,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="77" t="s">
+      <c r="A221" s="70" t="s">
         <v>279</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -6966,13 +6965,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="79"/>
+      <c r="A222" s="72"/>
       <c r="B222" s="41" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="77" t="s">
+      <c r="A223" s="70" t="s">
         <v>282</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -6980,31 +6979,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="78"/>
+      <c r="A224" s="71"/>
       <c r="B224" s="39" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="78"/>
+      <c r="A225" s="71"/>
       <c r="B225" s="39" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="78"/>
+      <c r="A226" s="71"/>
       <c r="B226" s="39" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="79"/>
+      <c r="A227" s="72"/>
       <c r="B227" s="41" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="77" t="s">
+      <c r="A228" s="70" t="s">
         <v>288</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -7012,31 +7011,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="78"/>
+      <c r="A229" s="71"/>
       <c r="B229" s="39" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="78"/>
+      <c r="A230" s="71"/>
       <c r="B230" s="39" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="78"/>
+      <c r="A231" s="71"/>
       <c r="B231" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="78"/>
+      <c r="A232" s="71"/>
       <c r="B232" s="39" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="79"/>
+      <c r="A233" s="72"/>
       <c r="B233" s="41" t="s">
         <v>294</v>
       </c>
@@ -7050,16 +7049,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="72" t="s">
+      <c r="A236" s="90" t="s">
         <v>297</v>
       </c>
-      <c r="B236" s="71"/>
+      <c r="B236" s="89"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="70" t="s">
+      <c r="A239" s="88" t="s">
         <v>298</v>
       </c>
-      <c r="B239" s="71"/>
+      <c r="B239" s="89"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -7158,10 +7157,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="73" t="s">
+      <c r="A257" s="91" t="s">
         <v>315</v>
       </c>
-      <c r="B257" s="74"/>
+      <c r="B257" s="92"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7338,10 +7337,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="80" t="s">
+      <c r="A288" s="77" t="s">
         <v>345</v>
       </c>
-      <c r="B288" s="81"/>
+      <c r="B288" s="78"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7532,14 +7531,22 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -7556,22 +7563,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7591,10 +7590,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="102" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="94"/>
+      <c r="B1" s="103"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7608,7 +7607,7 @@
       <c r="A3" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="96" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7616,25 +7615,25 @@
       <c r="A4" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="96"/>
+      <c r="B4" s="97"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="96"/>
+      <c r="B5" s="97"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="97"/>
+      <c r="B6" s="98"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="96" t="s">
         <v>382</v>
       </c>
     </row>
@@ -7642,25 +7641,25 @@
       <c r="A8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="96"/>
+      <c r="B8" s="97"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="96"/>
+      <c r="B9" s="97"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="97"/>
+      <c r="B10" s="98"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="96" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7668,85 +7667,85 @@
       <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="96"/>
+      <c r="B12" s="97"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="96"/>
+      <c r="B13" s="97"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="96"/>
+      <c r="B14" s="97"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="96"/>
+      <c r="B15" s="97"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="96"/>
+      <c r="B16" s="97"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="96"/>
+      <c r="B17" s="97"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="96"/>
+      <c r="B18" s="97"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="96"/>
+      <c r="B19" s="97"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="96"/>
+      <c r="B20" s="97"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="B21" s="96"/>
+      <c r="B21" s="97"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="96"/>
+      <c r="B22" s="97"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="98"/>
+      <c r="B23" s="104"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="99"/>
+      <c r="B24" s="105"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="96" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7754,61 +7753,61 @@
       <c r="A26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="96"/>
+      <c r="B26" s="97"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="96"/>
+      <c r="B27" s="97"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="96"/>
+      <c r="B28" s="97"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="96"/>
+      <c r="B29" s="97"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="96"/>
+      <c r="B30" s="97"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="96"/>
+      <c r="B31" s="97"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="96"/>
+      <c r="B32" s="97"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="96"/>
+      <c r="B33" s="97"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="97"/>
+      <c r="B34" s="98"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="95" t="s">
+      <c r="B35" s="96" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7816,13 +7815,13 @@
       <c r="A36" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="97"/>
+      <c r="B36" s="98"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="95" t="s">
+      <c r="B37" s="96" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7830,19 +7829,19 @@
       <c r="A38" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="96"/>
+      <c r="B38" s="97"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="96"/>
+      <c r="B39" s="97"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="96" t="s">
         <v>394</v>
       </c>
     </row>
@@ -7850,37 +7849,37 @@
       <c r="A41" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B41" s="96"/>
+      <c r="B41" s="97"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="96"/>
+      <c r="B42" s="97"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B43" s="96"/>
+      <c r="B43" s="97"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B44" s="96"/>
+      <c r="B44" s="97"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="96"/>
+      <c r="B45" s="97"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="97"/>
+      <c r="B46" s="98"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -7894,7 +7893,7 @@
       <c r="A48" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="95" t="s">
+      <c r="B48" s="96" t="s">
         <v>398</v>
       </c>
     </row>
@@ -7902,13 +7901,13 @@
       <c r="A49" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="97"/>
+      <c r="B49" s="98"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="95" t="s">
+      <c r="B50" s="96" t="s">
         <v>6</v>
       </c>
     </row>
@@ -7916,25 +7915,25 @@
       <c r="A51" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="96"/>
+      <c r="B51" s="97"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="96"/>
+      <c r="B52" s="97"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="96"/>
+      <c r="B53" s="97"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="97"/>
+      <c r="B54" s="98"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -7948,7 +7947,7 @@
       <c r="A56" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="95" t="s">
+      <c r="B56" s="96" t="s">
         <v>8</v>
       </c>
     </row>
@@ -7956,19 +7955,19 @@
       <c r="A57" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B57" s="96"/>
+      <c r="B57" s="97"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="97"/>
+      <c r="B58" s="98"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="95" t="s">
+      <c r="B59" s="96" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7976,37 +7975,37 @@
       <c r="A60" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="96"/>
+      <c r="B60" s="97"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="96"/>
+      <c r="B61" s="97"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="96"/>
+      <c r="B62" s="97"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="96"/>
+      <c r="B63" s="97"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="97"/>
+      <c r="B64" s="98"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B65" s="103" t="s">
+      <c r="B65" s="99" t="s">
         <v>402</v>
       </c>
     </row>
@@ -8014,26 +8013,26 @@
       <c r="A66" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="104"/>
+      <c r="B66" s="100"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="104"/>
+      <c r="B67" s="100"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="105"/>
+      <c r="B68" s="101"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="95" t="s">
+      <c r="B69" s="96" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8041,37 +8040,37 @@
       <c r="A70" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="96"/>
+      <c r="B70" s="97"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="96"/>
+      <c r="B71" s="97"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="96"/>
+      <c r="B72" s="97"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B73" s="96"/>
+      <c r="B73" s="97"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="97"/>
+      <c r="B74" s="98"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="95" t="s">
+      <c r="B75" s="96" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8079,139 +8078,139 @@
       <c r="A76" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="96"/>
+      <c r="B76" s="97"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="96"/>
+      <c r="B77" s="97"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="96"/>
+      <c r="B78" s="97"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="96"/>
+      <c r="B79" s="97"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="96"/>
+      <c r="B80" s="97"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="96"/>
+      <c r="B81" s="97"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B82" s="96"/>
+      <c r="B82" s="97"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="96"/>
+      <c r="B83" s="97"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B84" s="96"/>
+      <c r="B84" s="97"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="96"/>
+      <c r="B85" s="97"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="96"/>
+      <c r="B86" s="97"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="96"/>
+      <c r="B87" s="97"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="96"/>
+      <c r="B88" s="97"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="96"/>
+      <c r="B89" s="97"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="96"/>
+      <c r="B90" s="97"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="96"/>
+      <c r="B91" s="97"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="96"/>
+      <c r="B92" s="97"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="96"/>
+      <c r="B93" s="97"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="96"/>
+      <c r="B94" s="97"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="96"/>
+      <c r="B95" s="97"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="96"/>
+      <c r="B96" s="97"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B97" s="96"/>
+      <c r="B97" s="97"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="100" t="s">
+      <c r="B98" s="93" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8219,37 +8218,37 @@
       <c r="A99" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="101"/>
+      <c r="B99" s="94"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="101"/>
+      <c r="B100" s="94"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="101"/>
+      <c r="B101" s="94"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="101"/>
+      <c r="B102" s="94"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="101"/>
+      <c r="B103" s="94"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="102"/>
+      <c r="B104" s="95"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -8261,22 +8260,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepOtherInvestTargetInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepOtherInvestTargetInfo.xlsx
@@ -4743,6 +4743,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4750,18 +4771,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4788,28 +4797,40 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4822,15 +4843,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4838,18 +4850,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5433,7 +5433,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1 Y1 AI3:AI65518 Y3:Y65518 M3:M65518">
       <formula1>"01 是,02 否"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="L1 W1:X1 W3:X65518 L3:L65518"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="W3:X65518 W1:X1 L2"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="当选择“其他”时需注明" sqref="AA1 AA3:AA65518"/>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过3位，小数位不可超过5位" sqref="N1:N2">
       <formula1>-999.99999</formula1>
@@ -5497,7 +5497,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>枚举值!$A$7:$M$7</xm:f>
@@ -5515,6 +5515,12 @@
             <xm:f>各类资产应填要素列说明!$A$65:$A$68</xm:f>
           </x14:formula1>
           <xm:sqref>C1 C3:C1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写">
+          <x14:formula1>
+            <xm:f>国家或区域填写规则!$A$1:$A$239</xm:f>
+          </x14:formula1>
+          <xm:sqref>L1 L3:L1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5584,13 +5590,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="89"/>
+      <c r="B1" s="71"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="82" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5598,25 +5604,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="80"/>
+      <c r="A3" s="83"/>
       <c r="B3" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="80"/>
+      <c r="A4" s="83"/>
       <c r="B4" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="81"/>
+      <c r="A5" s="84"/>
       <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="85" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5624,13 +5630,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="83"/>
+      <c r="A7" s="86"/>
       <c r="B7" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="87" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5638,13 +5644,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="83"/>
+      <c r="A9" s="86"/>
       <c r="B9" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="75" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5652,61 +5658,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="86"/>
+      <c r="A11" s="88"/>
       <c r="B11" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="86"/>
+      <c r="A12" s="88"/>
       <c r="B12" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="86"/>
+      <c r="A13" s="88"/>
       <c r="B13" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="86"/>
+      <c r="A14" s="88"/>
       <c r="B14" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="86"/>
+      <c r="A15" s="88"/>
       <c r="B15" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="86"/>
+      <c r="A16" s="88"/>
       <c r="B16" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="86"/>
+      <c r="A17" s="88"/>
       <c r="B17" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="86"/>
+      <c r="A18" s="88"/>
       <c r="B18" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="86"/>
+      <c r="A19" s="88"/>
       <c r="B19" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="86"/>
+      <c r="A20" s="88"/>
       <c r="B20" s="15" t="s">
         <v>52</v>
       </c>
@@ -5720,7 +5726,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="75" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -5728,19 +5734,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="86"/>
+      <c r="A23" s="88"/>
       <c r="B23" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="87"/>
+      <c r="A24" s="76"/>
       <c r="B24" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="85" t="s">
+      <c r="A25" s="75" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -5748,67 +5754,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="86"/>
+      <c r="A26" s="88"/>
       <c r="B26" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="86"/>
+      <c r="A27" s="88"/>
       <c r="B27" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="86"/>
+      <c r="A28" s="88"/>
       <c r="B28" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="86"/>
+      <c r="A29" s="88"/>
       <c r="B29" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="86"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="86"/>
+      <c r="A31" s="88"/>
       <c r="B31" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="86"/>
+      <c r="A32" s="88"/>
       <c r="B32" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="86"/>
+      <c r="A33" s="88"/>
       <c r="B33" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="86"/>
+      <c r="A34" s="88"/>
       <c r="B34" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="87"/>
+      <c r="A35" s="76"/>
       <c r="B35" s="30" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="85" t="s">
+      <c r="A36" s="75" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -5816,25 +5822,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="86"/>
+      <c r="A37" s="88"/>
       <c r="B37" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="86"/>
+      <c r="A38" s="88"/>
       <c r="B38" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="87"/>
+      <c r="A39" s="76"/>
       <c r="B39" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="85" t="s">
+      <c r="A40" s="75" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -5842,43 +5848,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="86"/>
+      <c r="A41" s="88"/>
       <c r="B41" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="86"/>
+      <c r="A42" s="88"/>
       <c r="B42" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="86"/>
+      <c r="A43" s="88"/>
       <c r="B43" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="86"/>
+      <c r="A44" s="88"/>
       <c r="B44" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="86"/>
+      <c r="A45" s="88"/>
       <c r="B45" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="87"/>
+      <c r="A46" s="76"/>
       <c r="B46" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="85" t="s">
+      <c r="A47" s="75" t="s">
         <v>84</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -5886,61 +5892,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="86"/>
+      <c r="A48" s="88"/>
       <c r="B48" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="86"/>
+      <c r="A49" s="88"/>
       <c r="B49" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="86"/>
+      <c r="A50" s="88"/>
       <c r="B50" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="86"/>
+      <c r="A51" s="88"/>
       <c r="B51" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="86"/>
+      <c r="A52" s="88"/>
       <c r="B52" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="86"/>
+      <c r="A53" s="88"/>
       <c r="B53" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="86"/>
+      <c r="A54" s="88"/>
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="86"/>
+      <c r="A55" s="88"/>
       <c r="B55" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="87"/>
+      <c r="A56" s="76"/>
       <c r="B56" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="85" t="s">
+      <c r="A57" s="75" t="s">
         <v>95</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -5948,19 +5954,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="86"/>
+      <c r="A58" s="88"/>
       <c r="B58" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="87"/>
+      <c r="A59" s="76"/>
       <c r="B59" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="75" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -5968,37 +5974,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="86"/>
+      <c r="A61" s="88"/>
       <c r="B61" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="86"/>
+      <c r="A62" s="88"/>
       <c r="B62" s="24" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="86"/>
+      <c r="A63" s="88"/>
       <c r="B63" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="86"/>
+      <c r="A64" s="88"/>
       <c r="B64" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="87"/>
+      <c r="A65" s="76"/>
       <c r="B65" s="17" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="85" t="s">
+      <c r="A66" s="75" t="s">
         <v>106</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -6006,37 +6012,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="86"/>
+      <c r="A67" s="88"/>
       <c r="B67" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="86"/>
+      <c r="A68" s="88"/>
       <c r="B68" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="86"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="86"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="87"/>
+      <c r="A71" s="76"/>
       <c r="B71" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="85" t="s">
+      <c r="A72" s="75" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -6044,103 +6050,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="86"/>
+      <c r="A73" s="88"/>
       <c r="B73" s="10" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="86"/>
+      <c r="A74" s="88"/>
       <c r="B74" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="86"/>
+      <c r="A75" s="88"/>
       <c r="B75" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="86"/>
+      <c r="A76" s="88"/>
       <c r="B76" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="86"/>
+      <c r="A77" s="88"/>
       <c r="B77" s="25" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="86"/>
+      <c r="A78" s="88"/>
       <c r="B78" s="10" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="86"/>
+      <c r="A79" s="88"/>
       <c r="B79" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="86"/>
+      <c r="A80" s="88"/>
       <c r="B80" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="86"/>
+      <c r="A81" s="88"/>
       <c r="B81" s="25" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="86"/>
+      <c r="A82" s="88"/>
       <c r="B82" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="86"/>
+      <c r="A83" s="88"/>
       <c r="B83" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="86"/>
+      <c r="A84" s="88"/>
       <c r="B84" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="86"/>
+      <c r="A85" s="88"/>
       <c r="B85" s="25" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="86"/>
+      <c r="A86" s="88"/>
       <c r="B86" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="86"/>
+      <c r="A87" s="88"/>
       <c r="B87" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="87"/>
+      <c r="A88" s="76"/>
       <c r="B88" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="85" t="s">
+      <c r="A89" s="75" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -6148,38 +6154,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="86"/>
+      <c r="A90" s="88"/>
       <c r="B90" s="15" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="86"/>
+      <c r="A91" s="88"/>
       <c r="B91" s="15" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="86"/>
+      <c r="A92" s="88"/>
       <c r="B92" s="32" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="86"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="15" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="87"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="13" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="85" t="s">
+      <c r="A95" s="75" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -6187,43 +6193,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="86"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="25" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="86"/>
+      <c r="A97" s="88"/>
       <c r="B97" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="86"/>
+      <c r="A98" s="88"/>
       <c r="B98" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="86"/>
+      <c r="A99" s="88"/>
       <c r="B99" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="86"/>
+      <c r="A100" s="88"/>
       <c r="B100" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="87"/>
+      <c r="A101" s="76"/>
       <c r="B101" s="21" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="85" t="s">
+      <c r="A102" s="75" t="s">
         <v>146</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -6231,7 +6237,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="87"/>
+      <c r="A103" s="76"/>
       <c r="B103" s="13" t="s">
         <v>148</v>
       </c>
@@ -6249,10 +6255,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="88" t="s">
+      <c r="A107" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="B107" s="89"/>
+      <c r="B107" s="71"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6423,17 +6429,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="73" t="s">
+      <c r="A137" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="74"/>
+      <c r="B137" s="90"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="75"/>
-      <c r="B138" s="76"/>
+      <c r="A138" s="91"/>
+      <c r="B138" s="92"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="70" t="s">
+      <c r="A139" s="77" t="s">
         <v>181</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6441,31 +6447,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="71"/>
+      <c r="A140" s="78"/>
       <c r="B140" s="39" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="71"/>
+      <c r="A141" s="78"/>
       <c r="B141" s="39" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="71"/>
+      <c r="A142" s="78"/>
       <c r="B142" s="39" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="72"/>
+      <c r="A143" s="79"/>
       <c r="B143" s="41" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="70" t="s">
+      <c r="A144" s="77" t="s">
         <v>187</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6473,43 +6479,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="71"/>
+      <c r="A145" s="78"/>
       <c r="B145" s="39" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="71"/>
+      <c r="A146" s="78"/>
       <c r="B146" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="71"/>
+      <c r="A147" s="78"/>
       <c r="B147" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="71"/>
+      <c r="A148" s="78"/>
       <c r="B148" s="39" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="71"/>
+      <c r="A149" s="78"/>
       <c r="B149" s="39" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="72"/>
+      <c r="A150" s="79"/>
       <c r="B150" s="41" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="70" t="s">
+      <c r="A151" s="77" t="s">
         <v>195</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6517,187 +6523,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="71"/>
+      <c r="A152" s="78"/>
       <c r="B152" s="39" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="71"/>
+      <c r="A153" s="78"/>
       <c r="B153" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="71"/>
+      <c r="A154" s="78"/>
       <c r="B154" s="39" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="71"/>
+      <c r="A155" s="78"/>
       <c r="B155" s="39" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="71"/>
+      <c r="A156" s="78"/>
       <c r="B156" s="39" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="71"/>
+      <c r="A157" s="78"/>
       <c r="B157" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="71"/>
+      <c r="A158" s="78"/>
       <c r="B158" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="71"/>
+      <c r="A159" s="78"/>
       <c r="B159" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="71"/>
+      <c r="A160" s="78"/>
       <c r="B160" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="71"/>
+      <c r="A161" s="78"/>
       <c r="B161" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="71"/>
+      <c r="A162" s="78"/>
       <c r="B162" s="39" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="71"/>
+      <c r="A163" s="78"/>
       <c r="B163" s="39" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="71"/>
+      <c r="A164" s="78"/>
       <c r="B164" s="39" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="71"/>
+      <c r="A165" s="78"/>
       <c r="B165" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="71"/>
+      <c r="A166" s="78"/>
       <c r="B166" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="71"/>
+      <c r="A167" s="78"/>
       <c r="B167" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="71"/>
+      <c r="A168" s="78"/>
       <c r="B168" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="71"/>
+      <c r="A169" s="78"/>
       <c r="B169" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="71"/>
+      <c r="A170" s="78"/>
       <c r="B170" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="71"/>
+      <c r="A171" s="78"/>
       <c r="B171" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="71"/>
+      <c r="A172" s="78"/>
       <c r="B172" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="71"/>
+      <c r="A173" s="78"/>
       <c r="B173" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="71"/>
+      <c r="A174" s="78"/>
       <c r="B174" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="71"/>
+      <c r="A175" s="78"/>
       <c r="B175" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="71"/>
+      <c r="A176" s="78"/>
       <c r="B176" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="71"/>
+      <c r="A177" s="78"/>
       <c r="B177" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="71"/>
+      <c r="A178" s="78"/>
       <c r="B178" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="71"/>
+      <c r="A179" s="78"/>
       <c r="B179" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="71"/>
+      <c r="A180" s="78"/>
       <c r="B180" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="72"/>
+      <c r="A181" s="79"/>
       <c r="B181" s="41" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="70" t="s">
+      <c r="A182" s="77" t="s">
         <v>227</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6705,19 +6711,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="71"/>
+      <c r="A183" s="78"/>
       <c r="B183" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="72"/>
+      <c r="A184" s="79"/>
       <c r="B184" s="41" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="70" t="s">
+      <c r="A185" s="77" t="s">
         <v>231</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6725,25 +6731,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="71"/>
+      <c r="A186" s="78"/>
       <c r="B186" s="39" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="71"/>
+      <c r="A187" s="78"/>
       <c r="B187" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="72"/>
+      <c r="A188" s="79"/>
       <c r="B188" s="41" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="70" t="s">
+      <c r="A189" s="77" t="s">
         <v>236</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -6751,13 +6757,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="72"/>
+      <c r="A190" s="79"/>
       <c r="B190" s="41" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="70" t="s">
+      <c r="A191" s="77" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -6765,49 +6771,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="71"/>
+      <c r="A192" s="78"/>
       <c r="B192" s="39" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="71"/>
+      <c r="A193" s="78"/>
       <c r="B193" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="71"/>
+      <c r="A194" s="78"/>
       <c r="B194" s="39" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="71"/>
+      <c r="A195" s="78"/>
       <c r="B195" s="39" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="71"/>
+      <c r="A196" s="78"/>
       <c r="B196" s="39" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="71"/>
+      <c r="A197" s="78"/>
       <c r="B197" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="72"/>
+      <c r="A198" s="79"/>
       <c r="B198" s="41" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="70" t="s">
+      <c r="A199" s="77" t="s">
         <v>248</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -6815,13 +6821,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="72"/>
+      <c r="A200" s="79"/>
       <c r="B200" s="41" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="70" t="s">
+      <c r="A201" s="77" t="s">
         <v>251</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -6829,19 +6835,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="71"/>
+      <c r="A202" s="78"/>
       <c r="B202" s="39" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="72"/>
+      <c r="A203" s="79"/>
       <c r="B203" s="41" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="70" t="s">
+      <c r="A204" s="77" t="s">
         <v>255</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -6849,19 +6855,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="71"/>
+      <c r="A205" s="78"/>
       <c r="B205" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="71"/>
+      <c r="A206" s="78"/>
       <c r="B206" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="72"/>
+      <c r="A207" s="79"/>
       <c r="B207" s="41" t="s">
         <v>259</v>
       </c>
@@ -6875,7 +6881,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="70" t="s">
+      <c r="A209" s="77" t="s">
         <v>262</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -6883,13 +6889,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="72"/>
+      <c r="A210" s="79"/>
       <c r="B210" s="41" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="70" t="s">
+      <c r="A211" s="77" t="s">
         <v>265</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -6897,19 +6903,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="71"/>
+      <c r="A212" s="78"/>
       <c r="B212" s="39" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="72"/>
+      <c r="A213" s="79"/>
       <c r="B213" s="41" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="70" t="s">
+      <c r="A214" s="77" t="s">
         <v>269</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -6917,19 +6923,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="71"/>
+      <c r="A215" s="78"/>
       <c r="B215" s="39" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="72"/>
+      <c r="A216" s="79"/>
       <c r="B216" s="41" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="70" t="s">
+      <c r="A217" s="77" t="s">
         <v>273</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -6937,13 +6943,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="71"/>
+      <c r="A218" s="78"/>
       <c r="B218" s="39" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="72"/>
+      <c r="A219" s="79"/>
       <c r="B219" s="41" t="s">
         <v>276</v>
       </c>
@@ -6957,7 +6963,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="70" t="s">
+      <c r="A221" s="77" t="s">
         <v>279</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -6965,13 +6971,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="72"/>
+      <c r="A222" s="79"/>
       <c r="B222" s="41" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="70" t="s">
+      <c r="A223" s="77" t="s">
         <v>282</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -6979,31 +6985,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="71"/>
+      <c r="A224" s="78"/>
       <c r="B224" s="39" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="71"/>
+      <c r="A225" s="78"/>
       <c r="B225" s="39" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="71"/>
+      <c r="A226" s="78"/>
       <c r="B226" s="39" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="72"/>
+      <c r="A227" s="79"/>
       <c r="B227" s="41" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="70" t="s">
+      <c r="A228" s="77" t="s">
         <v>288</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -7011,31 +7017,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="71"/>
+      <c r="A229" s="78"/>
       <c r="B229" s="39" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="71"/>
+      <c r="A230" s="78"/>
       <c r="B230" s="39" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="71"/>
+      <c r="A231" s="78"/>
       <c r="B231" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="71"/>
+      <c r="A232" s="78"/>
       <c r="B232" s="39" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="72"/>
+      <c r="A233" s="79"/>
       <c r="B233" s="41" t="s">
         <v>294</v>
       </c>
@@ -7049,16 +7055,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="90" t="s">
+      <c r="A236" s="72" t="s">
         <v>297</v>
       </c>
-      <c r="B236" s="89"/>
+      <c r="B236" s="71"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="88" t="s">
+      <c r="A239" s="70" t="s">
         <v>298</v>
       </c>
-      <c r="B239" s="89"/>
+      <c r="B239" s="71"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -7157,10 +7163,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="91" t="s">
+      <c r="A257" s="73" t="s">
         <v>315</v>
       </c>
-      <c r="B257" s="92"/>
+      <c r="B257" s="74"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7337,10 +7343,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="77" t="s">
+      <c r="A288" s="80" t="s">
         <v>345</v>
       </c>
-      <c r="B288" s="78"/>
+      <c r="B288" s="81"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7531,6 +7537,30 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="A47:A56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="A72:A88"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="A95:A101"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A236:B236"/>
@@ -7547,30 +7577,6 @@
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="A201:A203"/>
     <mergeCell ref="A204:A207"/>
-    <mergeCell ref="A288:B288"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="A47:A56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="A72:A88"/>
-    <mergeCell ref="A89:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7590,10 +7596,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="93" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="103"/>
+      <c r="B1" s="94"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7607,7 +7613,7 @@
       <c r="A3" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="95" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7615,25 +7621,25 @@
       <c r="A4" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="97"/>
+      <c r="B4" s="96"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="97"/>
+      <c r="B5" s="96"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="98"/>
+      <c r="B6" s="97"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="95" t="s">
         <v>382</v>
       </c>
     </row>
@@ -7641,25 +7647,25 @@
       <c r="A8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="97"/>
+      <c r="B8" s="96"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="97"/>
+      <c r="B9" s="96"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="98"/>
+      <c r="B10" s="97"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="95" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7667,85 +7673,85 @@
       <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="97"/>
+      <c r="B12" s="96"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="97"/>
+      <c r="B13" s="96"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="97"/>
+      <c r="B14" s="96"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="97"/>
+      <c r="B15" s="96"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="97"/>
+      <c r="B16" s="96"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="97"/>
+      <c r="B17" s="96"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="97"/>
+      <c r="B18" s="96"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="97"/>
+      <c r="B19" s="96"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="97"/>
+      <c r="B20" s="96"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="B21" s="97"/>
+      <c r="B21" s="96"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="97"/>
+      <c r="B22" s="96"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="104"/>
+      <c r="B23" s="98"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="105"/>
+      <c r="B24" s="99"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="96" t="s">
+      <c r="B25" s="95" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7753,61 +7759,61 @@
       <c r="A26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="97"/>
+      <c r="B26" s="96"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="97"/>
+      <c r="B27" s="96"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="97"/>
+      <c r="B28" s="96"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="97"/>
+      <c r="B29" s="96"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="97"/>
+      <c r="B30" s="96"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="97"/>
+      <c r="B31" s="96"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="97"/>
+      <c r="B32" s="96"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="97"/>
+      <c r="B33" s="96"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="98"/>
+      <c r="B34" s="97"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="96" t="s">
+      <c r="B35" s="95" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7815,13 +7821,13 @@
       <c r="A36" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="98"/>
+      <c r="B36" s="97"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="96" t="s">
+      <c r="B37" s="95" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7829,19 +7835,19 @@
       <c r="A38" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="97"/>
+      <c r="B38" s="96"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="97"/>
+      <c r="B39" s="96"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="96" t="s">
+      <c r="B40" s="95" t="s">
         <v>394</v>
       </c>
     </row>
@@ -7849,37 +7855,37 @@
       <c r="A41" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B41" s="97"/>
+      <c r="B41" s="96"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="97"/>
+      <c r="B42" s="96"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B43" s="97"/>
+      <c r="B43" s="96"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B44" s="97"/>
+      <c r="B44" s="96"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="97"/>
+      <c r="B45" s="96"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="98"/>
+      <c r="B46" s="97"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -7893,7 +7899,7 @@
       <c r="A48" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="96" t="s">
+      <c r="B48" s="95" t="s">
         <v>398</v>
       </c>
     </row>
@@ -7901,13 +7907,13 @@
       <c r="A49" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="98"/>
+      <c r="B49" s="97"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="96" t="s">
+      <c r="B50" s="95" t="s">
         <v>6</v>
       </c>
     </row>
@@ -7915,25 +7921,25 @@
       <c r="A51" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="97"/>
+      <c r="B51" s="96"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="97"/>
+      <c r="B52" s="96"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="97"/>
+      <c r="B53" s="96"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="98"/>
+      <c r="B54" s="97"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -7947,7 +7953,7 @@
       <c r="A56" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="96" t="s">
+      <c r="B56" s="95" t="s">
         <v>8</v>
       </c>
     </row>
@@ -7955,19 +7961,19 @@
       <c r="A57" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B57" s="97"/>
+      <c r="B57" s="96"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="98"/>
+      <c r="B58" s="97"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="96" t="s">
+      <c r="B59" s="95" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7975,37 +7981,37 @@
       <c r="A60" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="97"/>
+      <c r="B60" s="96"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="97"/>
+      <c r="B61" s="96"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="97"/>
+      <c r="B62" s="96"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="97"/>
+      <c r="B63" s="96"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="98"/>
+      <c r="B64" s="97"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B65" s="99" t="s">
+      <c r="B65" s="103" t="s">
         <v>402</v>
       </c>
     </row>
@@ -8013,26 +8019,26 @@
       <c r="A66" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="100"/>
+      <c r="B66" s="104"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="100"/>
+      <c r="B67" s="104"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="101"/>
+      <c r="B68" s="105"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="96" t="s">
+      <c r="B69" s="95" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8040,37 +8046,37 @@
       <c r="A70" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="97"/>
+      <c r="B70" s="96"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="97"/>
+      <c r="B71" s="96"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="97"/>
+      <c r="B72" s="96"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B73" s="97"/>
+      <c r="B73" s="96"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="98"/>
+      <c r="B74" s="97"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="96" t="s">
+      <c r="B75" s="95" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8078,139 +8084,139 @@
       <c r="A76" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="97"/>
+      <c r="B76" s="96"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="97"/>
+      <c r="B77" s="96"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="97"/>
+      <c r="B78" s="96"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="97"/>
+      <c r="B79" s="96"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="97"/>
+      <c r="B80" s="96"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="97"/>
+      <c r="B81" s="96"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B82" s="97"/>
+      <c r="B82" s="96"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="97"/>
+      <c r="B83" s="96"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B84" s="97"/>
+      <c r="B84" s="96"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="97"/>
+      <c r="B85" s="96"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="97"/>
+      <c r="B86" s="96"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="97"/>
+      <c r="B87" s="96"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="97"/>
+      <c r="B88" s="96"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="97"/>
+      <c r="B89" s="96"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="97"/>
+      <c r="B90" s="96"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="97"/>
+      <c r="B91" s="96"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="97"/>
+      <c r="B92" s="96"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="97"/>
+      <c r="B93" s="96"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="97"/>
+      <c r="B94" s="96"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="97"/>
+      <c r="B95" s="96"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="97"/>
+      <c r="B96" s="96"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B97" s="97"/>
+      <c r="B97" s="96"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="93" t="s">
+      <c r="B98" s="100" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8218,37 +8224,37 @@
       <c r="A99" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="94"/>
+      <c r="B99" s="101"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="94"/>
+      <c r="B100" s="101"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="94"/>
+      <c r="B101" s="101"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="94"/>
+      <c r="B102" s="101"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="94"/>
+      <c r="B103" s="101"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="95"/>
+      <c r="B104" s="102"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -8260,22 +8266,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
